--- a/Code and data/Initial data/Non sector data/INST-QoG.xlsx
+++ b/Code and data/Initial data/Non sector data/INST-QoG.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L155"/>
+  <dimension ref="A1:M246"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -415,6 +415,11 @@
           <t>Value_Norm</t>
         </is>
       </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>EQI_Level</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -450,6 +455,11 @@
       <c r="K2">
         <v>0.787</v>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -485,6 +495,11 @@
       <c r="K3">
         <v>0.724</v>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -520,6 +535,11 @@
       <c r="K4">
         <v>0.86</v>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -555,6 +575,11 @@
       <c r="K5">
         <v>0.653</v>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -590,6 +615,11 @@
       <c r="K6">
         <v>0.76</v>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -625,6 +655,11 @@
       <c r="K7">
         <v>0.705</v>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -660,6 +695,11 @@
       <c r="K8">
         <v>0.894</v>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -695,6 +735,11 @@
       <c r="K9">
         <v>1.032</v>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -730,16 +775,21 @@
       <c r="K10">
         <v>1.084</v>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BG31</t>
+          <t>BE10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -763,18 +813,23 @@
         </is>
       </c>
       <c r="K11">
-        <v>-2.264</v>
+        <v>0.615692</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BG32</t>
+          <t>BE21</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -798,18 +853,23 @@
         </is>
       </c>
       <c r="K12">
-        <v>-0.997</v>
+        <v>0.615692</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BG33</t>
+          <t>BE22</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -833,18 +893,23 @@
         </is>
       </c>
       <c r="K13">
-        <v>-1.364</v>
+        <v>0.615692</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BG34</t>
+          <t>BE23</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -868,18 +933,23 @@
         </is>
       </c>
       <c r="K14">
-        <v>-2.189</v>
+        <v>0.615692</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BG41</t>
+          <t>BE24</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -903,18 +973,23 @@
         </is>
       </c>
       <c r="K15">
-        <v>-1.882</v>
+        <v>0.615692</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BG42</t>
+          <t>BE25</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -938,18 +1013,23 @@
         </is>
       </c>
       <c r="K16">
-        <v>-1.541</v>
+        <v>0.615692</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CZ01</t>
+          <t>BE31</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -973,18 +1053,23 @@
         </is>
       </c>
       <c r="K17">
-        <v>-0.163</v>
+        <v>0.615692</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CZ02</t>
+          <t>BE32</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1008,18 +1093,23 @@
         </is>
       </c>
       <c r="K18">
-        <v>-0.647</v>
+        <v>0.615692</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CZ03</t>
+          <t>BE33</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1043,18 +1133,23 @@
         </is>
       </c>
       <c r="K19">
-        <v>-0.291</v>
+        <v>0.615692</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CZ04</t>
+          <t>BE34</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1078,18 +1173,23 @@
         </is>
       </c>
       <c r="K20">
-        <v>-0.992</v>
+        <v>0.615692</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CZ05</t>
+          <t>BE35</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1113,18 +1213,23 @@
         </is>
       </c>
       <c r="K21">
-        <v>-0.171</v>
+        <v>0.615692</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CZ06</t>
+          <t>BG31</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1148,18 +1253,23 @@
         </is>
       </c>
       <c r="K22">
-        <v>0.015</v>
+        <v>-2.264</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CZ07</t>
+          <t>BG32</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1183,18 +1293,23 @@
         </is>
       </c>
       <c r="K23">
-        <v>-0.023</v>
+        <v>-0.997</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CZ08</t>
+          <t>BG33</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1218,18 +1333,23 @@
         </is>
       </c>
       <c r="K24">
-        <v>-0.276</v>
+        <v>-1.364</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DK01</t>
+          <t>BG34</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1253,18 +1373,23 @@
         </is>
       </c>
       <c r="K25">
-        <v>1.341</v>
+        <v>-2.189</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DK02</t>
+          <t>BG41</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1288,18 +1413,23 @@
         </is>
       </c>
       <c r="K26">
-        <v>1.23</v>
+        <v>-1.882</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DK03</t>
+          <t>BG42</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1323,18 +1453,23 @@
         </is>
       </c>
       <c r="K27">
-        <v>1.362</v>
+        <v>-1.541</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DK04</t>
+          <t>CY00</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1358,18 +1493,23 @@
         </is>
       </c>
       <c r="K28">
-        <v>1.648</v>
+        <v>-0.106</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>DK05</t>
+          <t>CZ01</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1393,18 +1533,23 @@
         </is>
       </c>
       <c r="K29">
-        <v>1.35</v>
+        <v>-0.163</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ES11</t>
+          <t>CZ02</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1428,18 +1573,23 @@
         </is>
       </c>
       <c r="K30">
-        <v>-0.432</v>
+        <v>-0.647</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ES12</t>
+          <t>CZ03</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1463,18 +1613,23 @@
         </is>
       </c>
       <c r="K31">
-        <v>0.218</v>
+        <v>-0.291</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ES13</t>
+          <t>CZ04</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1498,18 +1653,23 @@
         </is>
       </c>
       <c r="K32">
-        <v>0.423</v>
+        <v>-0.992</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ES21</t>
+          <t>CZ05</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1533,18 +1693,23 @@
         </is>
       </c>
       <c r="K33">
-        <v>0.652</v>
+        <v>-0.171</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ES22</t>
+          <t>CZ06</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1568,18 +1733,23 @@
         </is>
       </c>
       <c r="K34">
-        <v>0.502</v>
+        <v>0.015</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ES23</t>
+          <t>CZ07</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1603,18 +1773,23 @@
         </is>
       </c>
       <c r="K35">
-        <v>0.244</v>
+        <v>-0.023</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ES24</t>
+          <t>CZ08</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1638,18 +1813,23 @@
         </is>
       </c>
       <c r="K36">
-        <v>0.098</v>
+        <v>-0.276</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ES30</t>
+          <t>DE11</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1673,18 +1853,23 @@
         </is>
       </c>
       <c r="K37">
-        <v>-0.22</v>
+        <v>1.01313</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ES41</t>
+          <t>DE12</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1708,18 +1893,23 @@
         </is>
       </c>
       <c r="K38">
-        <v>-0.322</v>
+        <v>1.01313</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ES42</t>
+          <t>DE13</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1743,18 +1933,23 @@
         </is>
       </c>
       <c r="K39">
-        <v>-0.301</v>
+        <v>1.01313</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ES43</t>
+          <t>DE14</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1778,18 +1973,23 @@
         </is>
       </c>
       <c r="K40">
-        <v>0.023</v>
+        <v>1.01313</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ES51</t>
+          <t>DE21</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1813,18 +2013,23 @@
         </is>
       </c>
       <c r="K41">
-        <v>-0.392</v>
+        <v>1.01313</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ES52</t>
+          <t>DE22</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1848,18 +2053,23 @@
         </is>
       </c>
       <c r="K42">
-        <v>-0.445</v>
+        <v>1.01313</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ES53</t>
+          <t>DE23</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1883,18 +2093,23 @@
         </is>
       </c>
       <c r="K43">
-        <v>-0.545</v>
+        <v>1.01313</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ES61</t>
+          <t>DE24</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1918,18 +2133,23 @@
         </is>
       </c>
       <c r="K44">
-        <v>-0.739</v>
+        <v>1.01313</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ES62</t>
+          <t>DE25</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1953,18 +2173,23 @@
         </is>
       </c>
       <c r="K45">
-        <v>-0.136</v>
+        <v>1.01313</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ES70</t>
+          <t>DE26</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -1988,18 +2213,23 @@
         </is>
       </c>
       <c r="K46">
-        <v>-0.711</v>
+        <v>1.01313</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FI19</t>
+          <t>DE27</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2023,18 +2253,23 @@
         </is>
       </c>
       <c r="K47">
-        <v>1.336</v>
+        <v>1.01313</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FI1B</t>
+          <t>DE30</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2058,18 +2293,23 @@
         </is>
       </c>
       <c r="K48">
-        <v>1.495</v>
+        <v>1.01313</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FI1C</t>
+          <t>DE40</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2093,18 +2333,23 @@
         </is>
       </c>
       <c r="K49">
-        <v>1.406</v>
+        <v>1.01313</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FI1D</t>
+          <t>DE50</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2128,18 +2373,23 @@
         </is>
       </c>
       <c r="K50">
-        <v>1.442</v>
+        <v>1.01313</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FI20</t>
+          <t>DE60</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2163,18 +2413,23 @@
         </is>
       </c>
       <c r="K51">
-        <v>2.323</v>
+        <v>1.01313</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FR10</t>
+          <t>DE71</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2198,18 +2453,23 @@
         </is>
       </c>
       <c r="K52">
-        <v>0.498</v>
+        <v>1.01313</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FR91</t>
+          <t>DE72</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2233,18 +2493,23 @@
         </is>
       </c>
       <c r="K53">
-        <v>-1.03</v>
+        <v>1.01313</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FRB0</t>
+          <t>DE73</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2268,18 +2533,23 @@
         </is>
       </c>
       <c r="K54">
-        <v>0.42</v>
+        <v>1.01313</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FRC1</t>
+          <t>DE80</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2303,18 +2573,23 @@
         </is>
       </c>
       <c r="K55">
-        <v>0.283</v>
+        <v>1.01313</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FRC2</t>
+          <t>DE91</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2338,18 +2613,23 @@
         </is>
       </c>
       <c r="K56">
-        <v>0.185</v>
+        <v>1.01313</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FRD1</t>
+          <t>DE92</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2373,18 +2653,23 @@
         </is>
       </c>
       <c r="K57">
-        <v>0.39</v>
+        <v>1.01313</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>FRD2</t>
+          <t>DE93</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2408,18 +2693,23 @@
         </is>
       </c>
       <c r="K58">
-        <v>0.454</v>
+        <v>1.01313</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FRE1</t>
+          <t>DE94</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2443,18 +2733,23 @@
         </is>
       </c>
       <c r="K59">
-        <v>0.293</v>
+        <v>1.01313</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FRE2</t>
+          <t>DEA1</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2478,18 +2773,23 @@
         </is>
       </c>
       <c r="K60">
-        <v>0.407</v>
+        <v>1.01313</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FRF1</t>
+          <t>DEA2</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2513,18 +2813,23 @@
         </is>
       </c>
       <c r="K61">
-        <v>0.38</v>
+        <v>1.01313</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FRF2</t>
+          <t>DEA3</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2548,18 +2853,23 @@
         </is>
       </c>
       <c r="K62">
-        <v>0.338</v>
+        <v>1.01313</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>FRF3</t>
+          <t>DEA4</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2583,18 +2893,23 @@
         </is>
       </c>
       <c r="K63">
-        <v>0.238</v>
+        <v>1.01313</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>FRG0</t>
+          <t>DEA5</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2618,18 +2933,23 @@
         </is>
       </c>
       <c r="K64">
-        <v>0.719</v>
+        <v>1.01313</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>FRH0</t>
+          <t>DEB1</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2653,18 +2973,23 @@
         </is>
       </c>
       <c r="K65">
-        <v>0.769</v>
+        <v>1.01313</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>FRI1</t>
+          <t>DEB2</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2688,18 +3013,23 @@
         </is>
       </c>
       <c r="K66">
-        <v>0.695</v>
+        <v>1.01313</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>FRI2</t>
+          <t>DEB3</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2723,18 +3053,23 @@
         </is>
       </c>
       <c r="K67">
-        <v>0.619</v>
+        <v>1.01313</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>FRI3</t>
+          <t>DEC0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2758,18 +3093,23 @@
         </is>
       </c>
       <c r="K68">
-        <v>0.321</v>
+        <v>1.01313</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>FRJ1</t>
+          <t>DED2</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2793,18 +3133,23 @@
         </is>
       </c>
       <c r="K69">
-        <v>0.13</v>
+        <v>1.01313</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>FRJ2</t>
+          <t>DED4</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2828,18 +3173,23 @@
         </is>
       </c>
       <c r="K70">
-        <v>0.434</v>
+        <v>1.01313</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>FRK1</t>
+          <t>DED5</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2863,18 +3213,23 @@
         </is>
       </c>
       <c r="K71">
-        <v>0.441</v>
+        <v>1.01313</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>FRK2</t>
+          <t>DEE0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2898,18 +3253,23 @@
         </is>
       </c>
       <c r="K72">
-        <v>0.578</v>
+        <v>1.01313</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FRL0</t>
+          <t>DEF0</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2933,18 +3293,23 @@
         </is>
       </c>
       <c r="K73">
-        <v>0.213</v>
+        <v>1.01313</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>FRM0</t>
+          <t>DEG0</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -2968,18 +3333,23 @@
         </is>
       </c>
       <c r="K74">
-        <v>0.07199999999999999</v>
+        <v>1.01313</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>FRY2</t>
+          <t>DK01</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3003,18 +3373,23 @@
         </is>
       </c>
       <c r="K75">
-        <v>-0.726</v>
+        <v>1.341</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>FRY3</t>
+          <t>DK02</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3038,18 +3413,23 @@
         </is>
       </c>
       <c r="K76">
-        <v>-1.557</v>
+        <v>1.23</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>FRY4</t>
+          <t>DK03</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3073,18 +3453,23 @@
         </is>
       </c>
       <c r="K77">
-        <v>-0.413</v>
+        <v>1.362</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>HR03</t>
+          <t>DK04</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3108,18 +3493,23 @@
         </is>
       </c>
       <c r="K78">
-        <v>-1.156</v>
+        <v>1.648</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>HR04</t>
+          <t>DK05</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3143,18 +3533,23 @@
         </is>
       </c>
       <c r="K79">
-        <v>-1.239</v>
+        <v>1.35</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>HU10</t>
+          <t>EE00</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3178,18 +3573,23 @@
         </is>
       </c>
       <c r="K80">
-        <v>-1.455</v>
+        <v>0.231</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>HU21</t>
+          <t>EL30</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3213,18 +3613,23 @@
         </is>
       </c>
       <c r="K81">
-        <v>-0.969</v>
+        <v>-1.3873</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>HU22</t>
+          <t>EL41</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3248,18 +3653,23 @@
         </is>
       </c>
       <c r="K82">
-        <v>-1.016</v>
+        <v>-1.3873</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>HU23</t>
+          <t>EL42</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3283,18 +3693,23 @@
         </is>
       </c>
       <c r="K83">
-        <v>-0.98</v>
+        <v>-1.3873</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>HU31</t>
+          <t>EL43</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3318,18 +3733,23 @@
         </is>
       </c>
       <c r="K84">
-        <v>-1.089</v>
+        <v>-1.3873</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>HU32</t>
+          <t>EL51</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3353,18 +3773,23 @@
         </is>
       </c>
       <c r="K85">
-        <v>-1.266</v>
+        <v>-1.3873</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>HU33</t>
+          <t>EL52</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3388,18 +3813,23 @@
         </is>
       </c>
       <c r="K86">
-        <v>-0.748</v>
+        <v>-1.3873</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>IE01</t>
+          <t>EL53</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3423,18 +3853,23 @@
         </is>
       </c>
       <c r="K87">
-        <v>0.901</v>
+        <v>-1.3873</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>IE02</t>
+          <t>EL54</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3458,18 +3893,23 @@
         </is>
       </c>
       <c r="K88">
-        <v>0.8169999999999999</v>
+        <v>-1.3873</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ITC1</t>
+          <t>EL61</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3493,18 +3933,23 @@
         </is>
       </c>
       <c r="K89">
-        <v>-1.19</v>
+        <v>-1.3873</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ITC2</t>
+          <t>EL62</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3528,18 +3973,23 @@
         </is>
       </c>
       <c r="K90">
-        <v>-0.677</v>
+        <v>-1.3873</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ITC3</t>
+          <t>EL63</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3563,18 +4013,23 @@
         </is>
       </c>
       <c r="K91">
-        <v>-1.251</v>
+        <v>-1.3873</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ITC4</t>
+          <t>EL64</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3598,18 +4053,23 @@
         </is>
       </c>
       <c r="K92">
-        <v>-0.481</v>
+        <v>-1.3873</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ITF1</t>
+          <t>EL65</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3633,18 +4093,23 @@
         </is>
       </c>
       <c r="K93">
-        <v>-1.978</v>
+        <v>-1.3873</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ITF2</t>
+          <t>ES11</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3668,18 +4133,23 @@
         </is>
       </c>
       <c r="K94">
-        <v>-1.183</v>
+        <v>-0.432</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ITF3</t>
+          <t>ES12</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3703,18 +4173,23 @@
         </is>
       </c>
       <c r="K95">
-        <v>-1.877</v>
+        <v>0.218</v>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ITF4</t>
+          <t>ES13</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3738,18 +4213,23 @@
         </is>
       </c>
       <c r="K96">
-        <v>-1.545</v>
+        <v>0.423</v>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ITF5</t>
+          <t>ES21</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3773,18 +4253,23 @@
         </is>
       </c>
       <c r="K97">
-        <v>-1.668</v>
+        <v>0.652</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ITF6</t>
+          <t>ES22</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3808,18 +4293,23 @@
         </is>
       </c>
       <c r="K98">
-        <v>-2.183</v>
+        <v>0.502</v>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ITG1</t>
+          <t>ES23</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -3843,18 +4333,23 @@
         </is>
       </c>
       <c r="K99">
-        <v>-1.544</v>
+        <v>0.244</v>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ITG2</t>
+          <t>ES24</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -3878,18 +4373,23 @@
         </is>
       </c>
       <c r="K100">
-        <v>-1.234</v>
+        <v>0.098</v>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ITH1</t>
+          <t>ES30</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -3913,18 +4413,23 @@
         </is>
       </c>
       <c r="K101">
-        <v>-0.364</v>
+        <v>-0.22</v>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>ITH2</t>
+          <t>ES41</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -3948,18 +4453,23 @@
         </is>
       </c>
       <c r="K102">
-        <v>-0.364</v>
+        <v>-0.322</v>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ITH3</t>
+          <t>ES42</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -3983,18 +4493,23 @@
         </is>
       </c>
       <c r="K103">
-        <v>-0.459</v>
+        <v>-0.301</v>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ITH4</t>
+          <t>ES43</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4018,18 +4533,23 @@
         </is>
       </c>
       <c r="K104">
-        <v>-0.488</v>
+        <v>0.023</v>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ITH5</t>
+          <t>ES51</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4053,18 +4573,23 @@
         </is>
       </c>
       <c r="K105">
-        <v>-0.457</v>
+        <v>-0.392</v>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>ITI1</t>
+          <t>ES52</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -4088,18 +4613,23 @@
         </is>
       </c>
       <c r="K106">
-        <v>-0.849</v>
+        <v>-0.445</v>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ITI2</t>
+          <t>ES53</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -4123,18 +4653,23 @@
         </is>
       </c>
       <c r="K107">
-        <v>-1.51</v>
+        <v>-0.545</v>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>ITI3</t>
+          <t>ES61</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4158,18 +4693,23 @@
         </is>
       </c>
       <c r="K108">
-        <v>-1.383</v>
+        <v>-0.739</v>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ITI4</t>
+          <t>ES62</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4193,18 +4733,23 @@
         </is>
       </c>
       <c r="K109">
-        <v>-1.53</v>
+        <v>-0.136</v>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>NL11</t>
+          <t>ES63</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4228,18 +4773,23 @@
         </is>
       </c>
       <c r="K110">
-        <v>1.351</v>
+        <v>-0.327455</v>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, mismatched NUTS-2 codes)</t>
+        </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>NL12</t>
+          <t>ES64</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4263,18 +4813,23 @@
         </is>
       </c>
       <c r="K111">
-        <v>1.351</v>
+        <v>-0.327455</v>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, mismatched NUTS-2 codes)</t>
+        </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>NL13</t>
+          <t>ES70</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4298,18 +4853,23 @@
         </is>
       </c>
       <c r="K112">
-        <v>1.351</v>
+        <v>-0.711</v>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>NL21</t>
+          <t>FI19</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4333,18 +4893,23 @@
         </is>
       </c>
       <c r="K113">
-        <v>1.331</v>
+        <v>1.336</v>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>NL22</t>
+          <t>FI1B</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4368,18 +4933,23 @@
         </is>
       </c>
       <c r="K114">
-        <v>1.331</v>
+        <v>1.495</v>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>NL23</t>
+          <t>FI1C</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4403,18 +4973,23 @@
         </is>
       </c>
       <c r="K115">
-        <v>1.331</v>
+        <v>1.406</v>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>NL31</t>
+          <t>FI1D</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4438,18 +5013,23 @@
         </is>
       </c>
       <c r="K116">
-        <v>1.105</v>
+        <v>1.442</v>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>NL32</t>
+          <t>FI20</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -4473,18 +5053,23 @@
         </is>
       </c>
       <c r="K117">
-        <v>1.105</v>
+        <v>2.323</v>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>NL33</t>
+          <t>FR10</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -4508,18 +5093,23 @@
         </is>
       </c>
       <c r="K118">
-        <v>1.105</v>
+        <v>0.498</v>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>NL34</t>
+          <t>FR91</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -4543,18 +5133,23 @@
         </is>
       </c>
       <c r="K119">
-        <v>1.105</v>
+        <v>-1.03</v>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>NL41</t>
+          <t>FRB0</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -4578,18 +5173,23 @@
         </is>
       </c>
       <c r="K120">
-        <v>1.228</v>
+        <v>0.42</v>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>NL42</t>
+          <t>FRC1</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -4613,18 +5213,23 @@
         </is>
       </c>
       <c r="K121">
-        <v>1.228</v>
+        <v>0.283</v>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>PL21</t>
+          <t>FRC2</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -4648,18 +5253,23 @@
         </is>
       </c>
       <c r="K122">
-        <v>-0.401</v>
+        <v>0.185</v>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>PL22</t>
+          <t>FRD1</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -4683,18 +5293,23 @@
         </is>
       </c>
       <c r="K123">
-        <v>-0.48</v>
+        <v>0.39</v>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>PL41</t>
+          <t>FRD2</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -4718,18 +5333,23 @@
         </is>
       </c>
       <c r="K124">
-        <v>-0.464</v>
+        <v>0.454</v>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>PL42</t>
+          <t>FRE1</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -4753,18 +5373,23 @@
         </is>
       </c>
       <c r="K125">
-        <v>-0.367</v>
+        <v>0.293</v>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>PL43</t>
+          <t>FRE2</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -4788,18 +5413,23 @@
         </is>
       </c>
       <c r="K126">
-        <v>-0.411</v>
+        <v>0.407</v>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>PL51</t>
+          <t>FRF1</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -4823,18 +5453,23 @@
         </is>
       </c>
       <c r="K127">
-        <v>-0.482</v>
+        <v>0.38</v>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>PL52</t>
+          <t>FRF2</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -4858,18 +5493,23 @@
         </is>
       </c>
       <c r="K128">
-        <v>-0.298</v>
+        <v>0.338</v>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>PL61</t>
+          <t>FRF3</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -4893,18 +5533,23 @@
         </is>
       </c>
       <c r="K129">
-        <v>-0.338</v>
+        <v>0.238</v>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>PL62</t>
+          <t>FRG0</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -4928,18 +5573,23 @@
         </is>
       </c>
       <c r="K130">
-        <v>-0.342</v>
+        <v>0.719</v>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>PL63</t>
+          <t>FRH0</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -4963,18 +5613,23 @@
         </is>
       </c>
       <c r="K131">
-        <v>-0.133</v>
+        <v>0.769</v>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>PL71</t>
+          <t>FRI1</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -4998,18 +5653,23 @@
         </is>
       </c>
       <c r="K132">
-        <v>-0.66</v>
+        <v>0.695</v>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>PL72</t>
+          <t>FRI2</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -5033,18 +5693,23 @@
         </is>
       </c>
       <c r="K133">
-        <v>-0.511</v>
+        <v>0.619</v>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>PL81</t>
+          <t>FRI3</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -5068,18 +5733,23 @@
         </is>
       </c>
       <c r="K134">
-        <v>-0.632</v>
+        <v>0.321</v>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>PL82</t>
+          <t>FRJ1</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -5103,18 +5773,23 @@
         </is>
       </c>
       <c r="K135">
-        <v>-0.626</v>
+        <v>0.13</v>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>PL84</t>
+          <t>FRJ2</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -5138,18 +5813,23 @@
         </is>
       </c>
       <c r="K136">
-        <v>-0.456</v>
+        <v>0.434</v>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>PT11</t>
+          <t>FRK1</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -5173,18 +5853,23 @@
         </is>
       </c>
       <c r="K137">
-        <v>-0.063</v>
+        <v>0.441</v>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>PT15</t>
+          <t>FRK2</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -5208,18 +5893,23 @@
         </is>
       </c>
       <c r="K138">
-        <v>-0.292</v>
+        <v>0.578</v>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>PT16</t>
+          <t>FRL0</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -5243,18 +5933,23 @@
         </is>
       </c>
       <c r="K139">
-        <v>0.07000000000000001</v>
+        <v>0.213</v>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>PT17</t>
+          <t>FRM0</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -5278,18 +5973,23 @@
         </is>
       </c>
       <c r="K140">
-        <v>0.108</v>
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>PT18</t>
+          <t>FRY2</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -5313,18 +6013,23 @@
         </is>
       </c>
       <c r="K141">
-        <v>0.247</v>
+        <v>-0.726</v>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>PT20</t>
+          <t>FRY3</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -5348,18 +6053,23 @@
         </is>
       </c>
       <c r="K142">
-        <v>0.008999999999999999</v>
+        <v>-1.557</v>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>PT30</t>
+          <t>FRY4</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -5383,18 +6093,23 @@
         </is>
       </c>
       <c r="K143">
-        <v>0.169</v>
+        <v>-0.413</v>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>RO11</t>
+          <t>HR02</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -5418,18 +6133,23 @@
         </is>
       </c>
       <c r="K144">
-        <v>-1.849</v>
+        <v>-1.21138</v>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, mismatched NUTS-2 codes)</t>
+        </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>RO12</t>
+          <t>HR03</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -5453,18 +6173,23 @@
         </is>
       </c>
       <c r="K145">
-        <v>-1.434</v>
+        <v>-1.156</v>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>RO21</t>
+          <t>HR04</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -5488,18 +6213,23 @@
         </is>
       </c>
       <c r="K146">
-        <v>-1.58</v>
+        <v>-1.239</v>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>RO22</t>
+          <t>HR05</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -5523,18 +6253,23 @@
         </is>
       </c>
       <c r="K147">
-        <v>-1.973</v>
+        <v>-1.21138</v>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, mismatched NUTS-2 codes)</t>
+        </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>RO31</t>
+          <t>HR06</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -5558,18 +6293,23 @@
         </is>
       </c>
       <c r="K148">
-        <v>-1.104</v>
+        <v>-1.21138</v>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, mismatched NUTS-2 codes)</t>
+        </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>RO32</t>
+          <t>HU10</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -5593,18 +6333,23 @@
         </is>
       </c>
       <c r="K149">
-        <v>-1.578</v>
+        <v>-1.455</v>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>RO41</t>
+          <t>HU11</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -5628,18 +6373,23 @@
         </is>
       </c>
       <c r="K150">
-        <v>-1.615</v>
+        <v>-1.14995</v>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, mismatched NUTS-2 codes)</t>
+        </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>RO42</t>
+          <t>HU12</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -5663,18 +6413,23 @@
         </is>
       </c>
       <c r="K151">
-        <v>-1.341</v>
+        <v>-1.14995</v>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, mismatched NUTS-2 codes)</t>
+        </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>SK01</t>
+          <t>HU21</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -5698,18 +6453,23 @@
         </is>
       </c>
       <c r="K152">
-        <v>-0.954</v>
+        <v>-0.969</v>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>SK02</t>
+          <t>HU22</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -5733,18 +6493,23 @@
         </is>
       </c>
       <c r="K153">
-        <v>-1.013</v>
+        <v>-1.016</v>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>SK03</t>
+          <t>HU23</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -5768,42 +6533,3692 @@
         </is>
       </c>
       <c r="K154">
-        <v>-0.626</v>
+        <v>-0.98</v>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>HU31</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K155">
+        <v>-1.089</v>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>HU32</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K156">
+        <v>-1.266</v>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>HU33</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K157">
+        <v>-0.748</v>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>IE01</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K158">
+        <v>0.901</v>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>IE02</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K159">
+        <v>0.8169999999999999</v>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>IE04</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K160">
+        <v>0.839225</v>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, mismatched NUTS-2 codes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>IE05</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K161">
+        <v>0.839225</v>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, mismatched NUTS-2 codes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>IE06</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K162">
+        <v>0.839225</v>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, mismatched NUTS-2 codes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>ITC1</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K163">
+        <v>-1.19</v>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>ITC2</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K164">
+        <v>-0.677</v>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>ITC3</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K165">
+        <v>-1.251</v>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>ITC4</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K166">
+        <v>-0.481</v>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>ITF1</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K167">
+        <v>-1.978</v>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>ITF2</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K168">
+        <v>-1.183</v>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>ITF3</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K169">
+        <v>-1.877</v>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>ITF4</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K170">
+        <v>-1.545</v>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>ITF5</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K171">
+        <v>-1.668</v>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>ITF6</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K172">
+        <v>-2.183</v>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>ITG1</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K173">
+        <v>-1.544</v>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>ITG2</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K174">
+        <v>-1.234</v>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>ITH1</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K175">
+        <v>-0.364</v>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>ITH2</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K176">
+        <v>-0.364</v>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>ITH3</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K177">
+        <v>-0.459</v>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>ITH4</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K178">
+        <v>-0.488</v>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>ITH5</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K179">
+        <v>-0.457</v>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>ITI1</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K180">
+        <v>-0.849</v>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>ITI2</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K181">
+        <v>-1.51</v>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>ITI3</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K182">
+        <v>-1.383</v>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>ITI4</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K183">
+        <v>-1.53</v>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>LT01</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K184">
+        <v>-0.263</v>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>LT02</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K185">
+        <v>-0.263</v>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>LU00</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K186">
+        <v>1.2</v>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>LV</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>LV00</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K187">
+        <v>-0.513</v>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>MT00</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K188">
+        <v>-0.075</v>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>NL11</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K189">
+        <v>1.351</v>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>NL12</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K190">
+        <v>1.351</v>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>NL13</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K191">
+        <v>1.351</v>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>NL21</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K192">
+        <v>1.331</v>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>NL22</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K193">
+        <v>1.331</v>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>NL23</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K194">
+        <v>1.331</v>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>NL31</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K195">
+        <v>1.105</v>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>NL32</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K196">
+        <v>1.105</v>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>NL33</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K197">
+        <v>1.105</v>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>NL34</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K198">
+        <v>1.105</v>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>NL41</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K199">
+        <v>1.228</v>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>NL42</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K200">
+        <v>1.228</v>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>PL21</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K201">
+        <v>-0.401</v>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>PL22</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K202">
+        <v>-0.48</v>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>PL41</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K203">
+        <v>-0.464</v>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>PL42</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K204">
+        <v>-0.367</v>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>PL43</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K205">
+        <v>-0.411</v>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>PL51</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K206">
+        <v>-0.482</v>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>PL52</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K207">
+        <v>-0.298</v>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>PL61</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K208">
+        <v>-0.338</v>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>PL62</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K209">
+        <v>-0.342</v>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>PL63</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K210">
+        <v>-0.133</v>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>PL71</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K211">
+        <v>-0.66</v>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>PL72</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K212">
+        <v>-0.511</v>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>PL81</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K213">
+        <v>-0.632</v>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>PL82</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K214">
+        <v>-0.626</v>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>PL84</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K215">
+        <v>-0.456</v>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>PL91</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K216">
+        <v>-0.461115</v>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, mismatched NUTS-2 codes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>PL92</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K217">
+        <v>-0.461115</v>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, mismatched NUTS-2 codes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>PT11</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K218">
+        <v>-0.063</v>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>PT15</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K219">
+        <v>-0.292</v>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>PT16</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K220">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>PT17</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K221">
+        <v>0.108</v>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>PT18</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K222">
+        <v>0.247</v>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>PT20</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K223">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>PT30</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K224">
+        <v>0.169</v>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>RO11</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K225">
+        <v>-1.849</v>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>RO12</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K226">
+        <v>-1.434</v>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>RO21</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K227">
+        <v>-1.58</v>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>RO22</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K228">
+        <v>-1.973</v>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>RO31</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K229">
+        <v>-1.104</v>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>RO32</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K230">
+        <v>-1.578</v>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>RO41</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K231">
+        <v>-1.615</v>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>RO42</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K232">
+        <v>-1.341</v>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>SE11</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K233">
+        <v>1.40333</v>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>SE12</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K234">
+        <v>1.40333</v>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>SE21</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K235">
+        <v>1.40333</v>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>SE22</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K236">
+        <v>1.40333</v>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>SE23</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K237">
+        <v>1.40333</v>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>SE31</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K238">
+        <v>1.40333</v>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>SE32</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K239">
+        <v>1.40333</v>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>SE33</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K240">
+        <v>1.40333</v>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>SI03</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K241">
+        <v>-0.293</v>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>SI04</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K242">
+        <v>-0.293</v>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>NUTS-0 (national, replicated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>SK01</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K243">
+        <v>-0.954</v>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>SK02</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K244">
+        <v>-1.013</v>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>SK03</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K245">
+        <v>-0.626</v>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
         <is>
           <t>SK04</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>Vulnerability</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Institutions</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>QoG_Index</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>EQI Score</t>
-        </is>
-      </c>
-      <c r="K155">
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>QoG_Index</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>EQI Score</t>
+        </is>
+      </c>
+      <c r="K246">
         <v>-0.681</v>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>NUTS-2</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Code and data/Initial data/Non sector data/INST-QoG.xlsx
+++ b/Code and data/Initial data/Non sector data/INST-QoG.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M246"/>
+  <dimension ref="A1:M241"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -453,7 +453,7 @@
         </is>
       </c>
       <c r="K2">
-        <v>0.787</v>
+        <v>0.928</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>0.724</v>
+        <v>0.874</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="K4">
-        <v>0.86</v>
+        <v>0.757</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="K5">
-        <v>0.653</v>
+        <v>0.879</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="K6">
-        <v>0.76</v>
+        <v>0.976</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="K7">
-        <v>0.705</v>
+        <v>0.854</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="K8">
-        <v>0.894</v>
+        <v>1.119</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="K9">
-        <v>1.032</v>
+        <v>0.993</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="K10">
-        <v>1.084</v>
+        <v>0.925</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -813,11 +813,11 @@
         </is>
       </c>
       <c r="K11">
-        <v>0.615692</v>
+        <v>-0.13</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -853,11 +853,11 @@
         </is>
       </c>
       <c r="K12">
-        <v>0.615692</v>
+        <v>0.837</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -893,11 +893,11 @@
         </is>
       </c>
       <c r="K13">
-        <v>0.615692</v>
+        <v>0.837</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -933,11 +933,11 @@
         </is>
       </c>
       <c r="K14">
-        <v>0.615692</v>
+        <v>0.837</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -973,11 +973,11 @@
         </is>
       </c>
       <c r="K15">
-        <v>0.615692</v>
+        <v>0.837</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -1013,11 +1013,11 @@
         </is>
       </c>
       <c r="K16">
-        <v>0.615692</v>
+        <v>0.837</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -1053,11 +1053,11 @@
         </is>
       </c>
       <c r="K17">
-        <v>0.615692</v>
+        <v>0.602</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -1093,11 +1093,11 @@
         </is>
       </c>
       <c r="K18">
-        <v>0.615692</v>
+        <v>0.602</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -1133,11 +1133,11 @@
         </is>
       </c>
       <c r="K19">
-        <v>0.615692</v>
+        <v>0.602</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -1173,11 +1173,11 @@
         </is>
       </c>
       <c r="K20">
-        <v>0.615692</v>
+        <v>0.602</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -1213,11 +1213,11 @@
         </is>
       </c>
       <c r="K21">
-        <v>0.615692</v>
+        <v>0.602</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="K22">
-        <v>-2.264</v>
+        <v>-2.418</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="K23">
-        <v>-0.997</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="K24">
-        <v>-1.364</v>
+        <v>-0.973</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="K25">
-        <v>-2.189</v>
+        <v>-1.334</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="K26">
-        <v>-1.882</v>
+        <v>-1.926</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="K27">
-        <v>-1.541</v>
+        <v>-2.262</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="K28">
-        <v>-0.106</v>
+        <v>-0.556</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="K29">
-        <v>-0.163</v>
+        <v>0.029</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="K30">
-        <v>-0.647</v>
+        <v>-0.043</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="K31">
-        <v>-0.291</v>
+        <v>-0.188</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="K32">
-        <v>-0.992</v>
+        <v>-0.67</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         </is>
       </c>
       <c r="K33">
-        <v>-0.171</v>
+        <v>-0.1</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="K34">
-        <v>0.015</v>
+        <v>-0.092</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="K35">
-        <v>-0.023</v>
+        <v>-0.257</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="K36">
-        <v>-0.276</v>
+        <v>-0.179</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -1853,11 +1853,11 @@
         </is>
       </c>
       <c r="K37">
-        <v>1.01313</v>
+        <v>0.959</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -1893,11 +1893,11 @@
         </is>
       </c>
       <c r="K38">
-        <v>1.01313</v>
+        <v>0.959</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -1933,11 +1933,11 @@
         </is>
       </c>
       <c r="K39">
-        <v>1.01313</v>
+        <v>0.959</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -1973,11 +1973,11 @@
         </is>
       </c>
       <c r="K40">
-        <v>1.01313</v>
+        <v>0.959</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -2013,11 +2013,11 @@
         </is>
       </c>
       <c r="K41">
-        <v>1.01313</v>
+        <v>1.188</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -2053,11 +2053,11 @@
         </is>
       </c>
       <c r="K42">
-        <v>1.01313</v>
+        <v>1.188</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -2093,11 +2093,11 @@
         </is>
       </c>
       <c r="K43">
-        <v>1.01313</v>
+        <v>1.188</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -2133,11 +2133,11 @@
         </is>
       </c>
       <c r="K44">
-        <v>1.01313</v>
+        <v>1.188</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -2173,11 +2173,11 @@
         </is>
       </c>
       <c r="K45">
-        <v>1.01313</v>
+        <v>1.188</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -2213,11 +2213,11 @@
         </is>
       </c>
       <c r="K46">
-        <v>1.01313</v>
+        <v>1.188</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -2253,11 +2253,11 @@
         </is>
       </c>
       <c r="K47">
-        <v>1.01313</v>
+        <v>1.188</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -2293,11 +2293,11 @@
         </is>
       </c>
       <c r="K48">
-        <v>1.01313</v>
+        <v>0.444</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -2333,11 +2333,11 @@
         </is>
       </c>
       <c r="K49">
-        <v>1.01313</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -2373,11 +2373,11 @@
         </is>
       </c>
       <c r="K50">
-        <v>1.01313</v>
+        <v>0.513</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -2413,11 +2413,11 @@
         </is>
       </c>
       <c r="K51">
-        <v>1.01313</v>
+        <v>0.881</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -2453,11 +2453,11 @@
         </is>
       </c>
       <c r="K52">
-        <v>1.01313</v>
+        <v>1.155</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -2493,11 +2493,11 @@
         </is>
       </c>
       <c r="K53">
-        <v>1.01313</v>
+        <v>1.155</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -2533,11 +2533,11 @@
         </is>
       </c>
       <c r="K54">
-        <v>1.01313</v>
+        <v>1.155</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -2573,11 +2573,11 @@
         </is>
       </c>
       <c r="K55">
-        <v>1.01313</v>
+        <v>0.82</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -2613,11 +2613,11 @@
         </is>
       </c>
       <c r="K56">
-        <v>1.01313</v>
+        <v>1.1</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -2653,11 +2653,11 @@
         </is>
       </c>
       <c r="K57">
-        <v>1.01313</v>
+        <v>1.1</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -2693,11 +2693,11 @@
         </is>
       </c>
       <c r="K58">
-        <v>1.01313</v>
+        <v>1.1</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -2733,11 +2733,11 @@
         </is>
       </c>
       <c r="K59">
-        <v>1.01313</v>
+        <v>1.1</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -2773,11 +2773,11 @@
         </is>
       </c>
       <c r="K60">
-        <v>1.01313</v>
+        <v>0.854</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -2813,11 +2813,11 @@
         </is>
       </c>
       <c r="K61">
-        <v>1.01313</v>
+        <v>0.854</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -2853,11 +2853,11 @@
         </is>
       </c>
       <c r="K62">
-        <v>1.01313</v>
+        <v>0.854</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -2893,11 +2893,11 @@
         </is>
       </c>
       <c r="K63">
-        <v>1.01313</v>
+        <v>0.854</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -2933,11 +2933,11 @@
         </is>
       </c>
       <c r="K64">
-        <v>1.01313</v>
+        <v>0.854</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -2973,11 +2973,11 @@
         </is>
       </c>
       <c r="K65">
-        <v>1.01313</v>
+        <v>1.063</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -3013,11 +3013,11 @@
         </is>
       </c>
       <c r="K66">
-        <v>1.01313</v>
+        <v>1.063</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -3053,11 +3053,11 @@
         </is>
       </c>
       <c r="K67">
-        <v>1.01313</v>
+        <v>1.063</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -3093,11 +3093,11 @@
         </is>
       </c>
       <c r="K68">
-        <v>1.01313</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -3133,11 +3133,11 @@
         </is>
       </c>
       <c r="K69">
-        <v>1.01313</v>
+        <v>1.011</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -3173,11 +3173,11 @@
         </is>
       </c>
       <c r="K70">
-        <v>1.01313</v>
+        <v>1.011</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -3213,11 +3213,11 @@
         </is>
       </c>
       <c r="K71">
-        <v>1.01313</v>
+        <v>1.011</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -3253,11 +3253,11 @@
         </is>
       </c>
       <c r="K72">
-        <v>1.01313</v>
+        <v>0.723</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -3293,11 +3293,11 @@
         </is>
       </c>
       <c r="K73">
-        <v>1.01313</v>
+        <v>1.242</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -3333,11 +3333,11 @@
         </is>
       </c>
       <c r="K74">
-        <v>1.01313</v>
+        <v>0.859</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-1 (replicated)</t>
         </is>
       </c>
     </row>
@@ -3373,7 +3373,7 @@
         </is>
       </c>
       <c r="K75">
-        <v>1.341</v>
+        <v>1.557</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="K76">
-        <v>1.23</v>
+        <v>1.67</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         </is>
       </c>
       <c r="K77">
-        <v>1.362</v>
+        <v>1.856</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         </is>
       </c>
       <c r="K78">
-        <v>1.648</v>
+        <v>1.941</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="K79">
-        <v>1.35</v>
+        <v>2.104</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="K80">
-        <v>0.231</v>
+        <v>0.736</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -3613,11 +3613,11 @@
         </is>
       </c>
       <c r="K81">
-        <v>-1.3873</v>
+        <v>-1.298</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-2</t>
         </is>
       </c>
     </row>
@@ -3653,11 +3653,11 @@
         </is>
       </c>
       <c r="K82">
-        <v>-1.3873</v>
+        <v>-0.517</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-2</t>
         </is>
       </c>
     </row>
@@ -3693,11 +3693,11 @@
         </is>
       </c>
       <c r="K83">
-        <v>-1.3873</v>
+        <v>-0.907</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-2</t>
         </is>
       </c>
     </row>
@@ -3733,11 +3733,11 @@
         </is>
       </c>
       <c r="K84">
-        <v>-1.3873</v>
+        <v>-0.8</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-2</t>
         </is>
       </c>
     </row>
@@ -3773,11 +3773,11 @@
         </is>
       </c>
       <c r="K85">
-        <v>-1.3873</v>
+        <v>-0.918</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-2</t>
         </is>
       </c>
     </row>
@@ -3813,11 +3813,11 @@
         </is>
       </c>
       <c r="K86">
-        <v>-1.3873</v>
+        <v>-0.891</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-2</t>
         </is>
       </c>
     </row>
@@ -3853,11 +3853,11 @@
         </is>
       </c>
       <c r="K87">
-        <v>-1.3873</v>
+        <v>-0.197</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-2</t>
         </is>
       </c>
     </row>
@@ -3893,11 +3893,11 @@
         </is>
       </c>
       <c r="K88">
-        <v>-1.3873</v>
+        <v>-0.681</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-2</t>
         </is>
       </c>
     </row>
@@ -3933,11 +3933,11 @@
         </is>
       </c>
       <c r="K89">
-        <v>-1.3873</v>
+        <v>-0.44</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-2</t>
         </is>
       </c>
     </row>
@@ -3973,11 +3973,11 @@
         </is>
       </c>
       <c r="K90">
-        <v>-1.3873</v>
+        <v>-0.55</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-2</t>
         </is>
       </c>
     </row>
@@ -4013,11 +4013,11 @@
         </is>
       </c>
       <c r="K91">
-        <v>-1.3873</v>
+        <v>-1.239</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-2</t>
         </is>
       </c>
     </row>
@@ -4053,11 +4053,11 @@
         </is>
       </c>
       <c r="K92">
-        <v>-1.3873</v>
+        <v>-1.018</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-2</t>
         </is>
       </c>
     </row>
@@ -4093,11 +4093,11 @@
         </is>
       </c>
       <c r="K93">
-        <v>-1.3873</v>
+        <v>-1.108</v>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-2</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
         </is>
       </c>
       <c r="K94">
-        <v>-0.432</v>
+        <v>-0.387</v>
       </c>
       <c r="M94" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="K95">
-        <v>0.218</v>
+        <v>0.061</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c r="K96">
-        <v>0.423</v>
+        <v>0.623</v>
       </c>
       <c r="M96" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="K97">
-        <v>0.652</v>
+        <v>0.051</v>
       </c>
       <c r="M97" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         </is>
       </c>
       <c r="K98">
-        <v>0.502</v>
+        <v>0.048</v>
       </c>
       <c r="M98" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         </is>
       </c>
       <c r="K99">
-        <v>0.244</v>
+        <v>0.213</v>
       </c>
       <c r="M99" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         </is>
       </c>
       <c r="K100">
-        <v>0.098</v>
+        <v>0.035</v>
       </c>
       <c r="M100" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="K101">
-        <v>-0.22</v>
+        <v>0.339</v>
       </c>
       <c r="M101" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         </is>
       </c>
       <c r="K102">
-        <v>-0.322</v>
+        <v>-1.242</v>
       </c>
       <c r="M102" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="K103">
-        <v>-0.301</v>
+        <v>0.028</v>
       </c>
       <c r="M103" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         </is>
       </c>
       <c r="K104">
-        <v>0.023</v>
+        <v>-0.764</v>
       </c>
       <c r="M104" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         </is>
       </c>
       <c r="K105">
-        <v>-0.392</v>
+        <v>-0.232</v>
       </c>
       <c r="M105" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         </is>
       </c>
       <c r="K106">
-        <v>-0.445</v>
+        <v>-0.181</v>
       </c>
       <c r="M106" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="K107">
-        <v>-0.545</v>
+        <v>-0.263</v>
       </c>
       <c r="M107" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="K108">
-        <v>-0.739</v>
+        <v>-0.764</v>
       </c>
       <c r="M108" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="K109">
-        <v>-0.136</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="M109" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ES63</t>
+          <t>ES70</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4773,23 +4773,23 @@
         </is>
       </c>
       <c r="K110">
-        <v>-0.327455</v>
+        <v>-0.139</v>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, mismatched NUTS-2 codes)</t>
+          <t>NUTS-2</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>ES64</t>
+          <t>FI19</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4813,23 +4813,23 @@
         </is>
       </c>
       <c r="K111">
-        <v>-0.327455</v>
+        <v>1.542</v>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, mismatched NUTS-2 codes)</t>
+          <t>NUTS-2</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>ES70</t>
+          <t>FI1B</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="K112">
-        <v>-0.711</v>
+        <v>1.559</v>
       </c>
       <c r="M112" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>FI19</t>
+          <t>FI1C</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4893,7 +4893,7 @@
         </is>
       </c>
       <c r="K113">
-        <v>1.336</v>
+        <v>1.627</v>
       </c>
       <c r="M113" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>FI1B</t>
+          <t>FI1D</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="K114">
-        <v>1.495</v>
+        <v>1.935</v>
       </c>
       <c r="M114" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>FI1C</t>
+          <t>FI20</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4973,7 +4973,7 @@
         </is>
       </c>
       <c r="K115">
-        <v>1.406</v>
+        <v>2.585</v>
       </c>
       <c r="M115" t="inlineStr">
         <is>
@@ -4984,12 +4984,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>FI1D</t>
+          <t>FR10</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -5013,7 +5013,7 @@
         </is>
       </c>
       <c r="K116">
-        <v>1.442</v>
+        <v>0.023</v>
       </c>
       <c r="M116" t="inlineStr">
         <is>
@@ -5024,12 +5024,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>FI20</t>
+          <t>FRB0</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -5053,7 +5053,7 @@
         </is>
       </c>
       <c r="K117">
-        <v>2.323</v>
+        <v>0.384</v>
       </c>
       <c r="M117" t="inlineStr">
         <is>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>FR10</t>
+          <t>FRC1</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -5093,7 +5093,7 @@
         </is>
       </c>
       <c r="K118">
-        <v>0.498</v>
+        <v>0.458</v>
       </c>
       <c r="M118" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>FR91</t>
+          <t>FRC2</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -5133,7 +5133,7 @@
         </is>
       </c>
       <c r="K119">
-        <v>-1.03</v>
+        <v>0.492</v>
       </c>
       <c r="M119" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>FRB0</t>
+          <t>FRD1</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="K120">
-        <v>0.42</v>
+        <v>0.579</v>
       </c>
       <c r="M120" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>FRC1</t>
+          <t>FRD2</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -5213,7 +5213,7 @@
         </is>
       </c>
       <c r="K121">
-        <v>0.283</v>
+        <v>0.427</v>
       </c>
       <c r="M121" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>FRC2</t>
+          <t>FRE1</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -5253,7 +5253,7 @@
         </is>
       </c>
       <c r="K122">
-        <v>0.185</v>
+        <v>0.451</v>
       </c>
       <c r="M122" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>FRD1</t>
+          <t>FRE2</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -5293,7 +5293,7 @@
         </is>
       </c>
       <c r="K123">
-        <v>0.39</v>
+        <v>0.198</v>
       </c>
       <c r="M123" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>FRD2</t>
+          <t>FRF1</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="K124">
-        <v>0.454</v>
+        <v>0.569</v>
       </c>
       <c r="M124" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>FRE1</t>
+          <t>FRF2</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -5373,7 +5373,7 @@
         </is>
       </c>
       <c r="K125">
-        <v>0.293</v>
+        <v>0.213</v>
       </c>
       <c r="M125" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>FRE2</t>
+          <t>FRF3</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="K126">
-        <v>0.407</v>
+        <v>0.356</v>
       </c>
       <c r="M126" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>FRF1</t>
+          <t>FRG0</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -5453,7 +5453,7 @@
         </is>
       </c>
       <c r="K127">
-        <v>0.38</v>
+        <v>0.778</v>
       </c>
       <c r="M127" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>FRF2</t>
+          <t>FRH0</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -5493,7 +5493,7 @@
         </is>
       </c>
       <c r="K128">
-        <v>0.338</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="M128" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>FRF3</t>
+          <t>FRI1</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="K129">
-        <v>0.238</v>
+        <v>0.739</v>
       </c>
       <c r="M129" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>FRG0</t>
+          <t>FRI2</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -5573,7 +5573,7 @@
         </is>
       </c>
       <c r="K130">
-        <v>0.719</v>
+        <v>0.584</v>
       </c>
       <c r="M130" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>FRH0</t>
+          <t>FRI3</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -5613,7 +5613,7 @@
         </is>
       </c>
       <c r="K131">
-        <v>0.769</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="M131" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>FRI1</t>
+          <t>FRJ1</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="K132">
-        <v>0.695</v>
+        <v>0.202</v>
       </c>
       <c r="M132" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>FRI2</t>
+          <t>FRJ2</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="K133">
-        <v>0.619</v>
+        <v>0.569</v>
       </c>
       <c r="M133" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>FRI3</t>
+          <t>FRK1</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -5733,7 +5733,7 @@
         </is>
       </c>
       <c r="K134">
-        <v>0.321</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="M134" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>FRJ1</t>
+          <t>FRK2</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -5773,7 +5773,7 @@
         </is>
       </c>
       <c r="K135">
-        <v>0.13</v>
+        <v>0.477</v>
       </c>
       <c r="M135" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>FRJ2</t>
+          <t>FRL0</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -5813,7 +5813,7 @@
         </is>
       </c>
       <c r="K136">
-        <v>0.434</v>
+        <v>0.118</v>
       </c>
       <c r="M136" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>FRK1</t>
+          <t>FRM0</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -5853,7 +5853,7 @@
         </is>
       </c>
       <c r="K137">
-        <v>0.441</v>
+        <v>0.435</v>
       </c>
       <c r="M137" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>FRK2</t>
+          <t>FRY1</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -5893,7 +5893,7 @@
         </is>
       </c>
       <c r="K138">
-        <v>0.578</v>
+        <v>-0.965</v>
       </c>
       <c r="M138" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>FRL0</t>
+          <t>FRY2</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="K139">
-        <v>0.213</v>
+        <v>-0.506</v>
       </c>
       <c r="M139" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>FRM0</t>
+          <t>FRY3</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -5973,7 +5973,7 @@
         </is>
       </c>
       <c r="K140">
-        <v>0.07199999999999999</v>
+        <v>-0.962</v>
       </c>
       <c r="M140" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>FRY2</t>
+          <t>FRY4</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -6013,7 +6013,7 @@
         </is>
       </c>
       <c r="K141">
-        <v>-0.726</v>
+        <v>0.012</v>
       </c>
       <c r="M141" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>FRY3</t>
+          <t>FRY5</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -6053,7 +6053,7 @@
         </is>
       </c>
       <c r="K142">
-        <v>-1.557</v>
+        <v>-1.171</v>
       </c>
       <c r="M142" t="inlineStr">
         <is>
@@ -6064,12 +6064,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>FRY4</t>
+          <t>HR02</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -6093,7 +6093,7 @@
         </is>
       </c>
       <c r="K143">
-        <v>-0.413</v>
+        <v>-1.082</v>
       </c>
       <c r="M143" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>HR02</t>
+          <t>HR03</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -6133,11 +6133,11 @@
         </is>
       </c>
       <c r="K144">
-        <v>-1.21138</v>
+        <v>-0.854</v>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, mismatched NUTS-2 codes)</t>
+          <t>NUTS-2</t>
         </is>
       </c>
     </row>
@@ -6149,7 +6149,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>HR03</t>
+          <t>HR05</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="K145">
-        <v>-1.156</v>
+        <v>-1.348</v>
       </c>
       <c r="M145" t="inlineStr">
         <is>
@@ -6189,7 +6189,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>HR04</t>
+          <t>HR06</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -6213,7 +6213,7 @@
         </is>
       </c>
       <c r="K146">
-        <v>-1.239</v>
+        <v>-0.662</v>
       </c>
       <c r="M146" t="inlineStr">
         <is>
@@ -6224,12 +6224,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>HR05</t>
+          <t>HU11</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -6253,23 +6253,23 @@
         </is>
       </c>
       <c r="K147">
-        <v>-1.21138</v>
+        <v>-1.15</v>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, mismatched NUTS-2 codes)</t>
+          <t>NUTS-2</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>HR06</t>
+          <t>HU12</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -6293,11 +6293,11 @@
         </is>
       </c>
       <c r="K148">
-        <v>-1.21138</v>
+        <v>-1.08</v>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, mismatched NUTS-2 codes)</t>
+          <t>NUTS-2</t>
         </is>
       </c>
     </row>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>HU10</t>
+          <t>HU21</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="K149">
-        <v>-1.455</v>
+        <v>-0.893</v>
       </c>
       <c r="M149" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>HU11</t>
+          <t>HU22</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -6373,11 +6373,11 @@
         </is>
       </c>
       <c r="K150">
-        <v>-1.14995</v>
+        <v>-1.137</v>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, mismatched NUTS-2 codes)</t>
+          <t>NUTS-2</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>HU12</t>
+          <t>HU23</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -6413,11 +6413,11 @@
         </is>
       </c>
       <c r="K151">
-        <v>-1.14995</v>
+        <v>-1.181</v>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, mismatched NUTS-2 codes)</t>
+          <t>NUTS-2</t>
         </is>
       </c>
     </row>
@@ -6429,7 +6429,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>HU21</t>
+          <t>HU31</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -6453,7 +6453,7 @@
         </is>
       </c>
       <c r="K152">
-        <v>-0.969</v>
+        <v>-1.276</v>
       </c>
       <c r="M152" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>HU22</t>
+          <t>HU32</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -6493,7 +6493,7 @@
         </is>
       </c>
       <c r="K153">
-        <v>-1.016</v>
+        <v>-1.462</v>
       </c>
       <c r="M153" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>HU23</t>
+          <t>HU33</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -6533,7 +6533,7 @@
         </is>
       </c>
       <c r="K154">
-        <v>-0.98</v>
+        <v>-1.191</v>
       </c>
       <c r="M154" t="inlineStr">
         <is>
@@ -6544,12 +6544,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>HU31</t>
+          <t>IE04</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="K155">
-        <v>-1.089</v>
+        <v>1.014</v>
       </c>
       <c r="M155" t="inlineStr">
         <is>
@@ -6584,12 +6584,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>HU32</t>
+          <t>IE05</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -6613,7 +6613,7 @@
         </is>
       </c>
       <c r="K156">
-        <v>-1.266</v>
+        <v>1.175</v>
       </c>
       <c r="M156" t="inlineStr">
         <is>
@@ -6624,12 +6624,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>HU33</t>
+          <t>IE06</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -6653,7 +6653,7 @@
         </is>
       </c>
       <c r="K157">
-        <v>-0.748</v>
+        <v>0.917</v>
       </c>
       <c r="M157" t="inlineStr">
         <is>
@@ -6664,12 +6664,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>IE01</t>
+          <t>ITC1</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -6693,7 +6693,7 @@
         </is>
       </c>
       <c r="K158">
-        <v>0.901</v>
+        <v>-0.28</v>
       </c>
       <c r="M158" t="inlineStr">
         <is>
@@ -6704,12 +6704,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>IE02</t>
+          <t>ITC2</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -6733,7 +6733,7 @@
         </is>
       </c>
       <c r="K159">
-        <v>0.8169999999999999</v>
+        <v>-0.127</v>
       </c>
       <c r="M159" t="inlineStr">
         <is>
@@ -6744,12 +6744,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>IE04</t>
+          <t>ITC3</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -6773,23 +6773,23 @@
         </is>
       </c>
       <c r="K160">
-        <v>0.839225</v>
+        <v>0.081</v>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, mismatched NUTS-2 codes)</t>
+          <t>NUTS-2</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>IE05</t>
+          <t>ITC4</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -6813,23 +6813,23 @@
         </is>
       </c>
       <c r="K161">
-        <v>0.839225</v>
+        <v>-0.225</v>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, mismatched NUTS-2 codes)</t>
+          <t>NUTS-2</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>IE06</t>
+          <t>ITF1</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -6853,11 +6853,11 @@
         </is>
       </c>
       <c r="K162">
-        <v>0.839225</v>
+        <v>-0.903</v>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, mismatched NUTS-2 codes)</t>
+          <t>NUTS-2</t>
         </is>
       </c>
     </row>
@@ -6869,7 +6869,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>ITC1</t>
+          <t>ITF2</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -6893,7 +6893,7 @@
         </is>
       </c>
       <c r="K163">
-        <v>-1.19</v>
+        <v>-1.938</v>
       </c>
       <c r="M163" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>ITC2</t>
+          <t>ITF3</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -6933,7 +6933,7 @@
         </is>
       </c>
       <c r="K164">
-        <v>-0.677</v>
+        <v>-1.215</v>
       </c>
       <c r="M164" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>ITC3</t>
+          <t>ITF4</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -6973,7 +6973,7 @@
         </is>
       </c>
       <c r="K165">
-        <v>-1.251</v>
+        <v>-1.266</v>
       </c>
       <c r="M165" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>ITC4</t>
+          <t>ITF5</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -7013,7 +7013,7 @@
         </is>
       </c>
       <c r="K166">
-        <v>-0.481</v>
+        <v>-1.079</v>
       </c>
       <c r="M166" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>ITF1</t>
+          <t>ITF6</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="K167">
-        <v>-1.978</v>
+        <v>-1.278</v>
       </c>
       <c r="M167" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>ITF2</t>
+          <t>ITG1</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -7093,7 +7093,7 @@
         </is>
       </c>
       <c r="K168">
-        <v>-1.183</v>
+        <v>-2.059</v>
       </c>
       <c r="M168" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>ITF3</t>
+          <t>ITG2</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -7133,7 +7133,7 @@
         </is>
       </c>
       <c r="K169">
-        <v>-1.877</v>
+        <v>-0.225</v>
       </c>
       <c r="M169" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>ITF4</t>
+          <t>ITH1</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -7173,7 +7173,7 @@
         </is>
       </c>
       <c r="K170">
-        <v>-1.545</v>
+        <v>0.075</v>
       </c>
       <c r="M170" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>ITF5</t>
+          <t>ITH2</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -7213,7 +7213,7 @@
         </is>
       </c>
       <c r="K171">
-        <v>-1.668</v>
+        <v>0.411</v>
       </c>
       <c r="M171" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>ITF6</t>
+          <t>ITH3</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -7253,7 +7253,7 @@
         </is>
       </c>
       <c r="K172">
-        <v>-2.183</v>
+        <v>-0.403</v>
       </c>
       <c r="M172" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>ITG1</t>
+          <t>ITH4</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -7293,7 +7293,7 @@
         </is>
       </c>
       <c r="K173">
-        <v>-1.544</v>
+        <v>0.718</v>
       </c>
       <c r="M173" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>ITG2</t>
+          <t>ITH5</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -7333,7 +7333,7 @@
         </is>
       </c>
       <c r="K174">
-        <v>-1.234</v>
+        <v>-1.102</v>
       </c>
       <c r="M174" t="inlineStr">
         <is>
@@ -7349,7 +7349,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>ITH1</t>
+          <t>ITI1</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -7373,7 +7373,7 @@
         </is>
       </c>
       <c r="K175">
-        <v>-0.364</v>
+        <v>-0.514</v>
       </c>
       <c r="M175" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>ITH2</t>
+          <t>ITI2</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -7413,7 +7413,7 @@
         </is>
       </c>
       <c r="K176">
-        <v>-0.364</v>
+        <v>-0.945</v>
       </c>
       <c r="M176" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>ITH3</t>
+          <t>ITI3</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -7453,7 +7453,7 @@
         </is>
       </c>
       <c r="K177">
-        <v>-0.459</v>
+        <v>-0.152</v>
       </c>
       <c r="M177" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>ITH4</t>
+          <t>ITI4</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -7493,7 +7493,7 @@
         </is>
       </c>
       <c r="K178">
-        <v>-0.488</v>
+        <v>-1.068</v>
       </c>
       <c r="M178" t="inlineStr">
         <is>
@@ -7504,12 +7504,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>ITH5</t>
+          <t>LT01</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -7533,7 +7533,7 @@
         </is>
       </c>
       <c r="K179">
-        <v>-0.457</v>
+        <v>0.191</v>
       </c>
       <c r="M179" t="inlineStr">
         <is>
@@ -7544,12 +7544,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>ITI1</t>
+          <t>LT02</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -7573,7 +7573,7 @@
         </is>
       </c>
       <c r="K180">
-        <v>-0.849</v>
+        <v>-0.104</v>
       </c>
       <c r="M180" t="inlineStr">
         <is>
@@ -7584,12 +7584,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>ITI2</t>
+          <t>LU00</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -7613,23 +7613,23 @@
         </is>
       </c>
       <c r="K181">
-        <v>-1.51</v>
+        <v>1.305</v>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>NUTS-2</t>
+          <t>NUTS-0 (national, replicated)</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>ITI3</t>
+          <t>LV00</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -7653,23 +7653,23 @@
         </is>
       </c>
       <c r="K182">
-        <v>-1.383</v>
+        <v>-0.227</v>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>NUTS-2</t>
+          <t>NUTS-0 (national, replicated)</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>ITI4</t>
+          <t>MT00</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -7693,23 +7693,23 @@
         </is>
       </c>
       <c r="K183">
-        <v>-1.53</v>
+        <v>-0.471</v>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>NUTS-2</t>
+          <t>NUTS-0 (national, replicated)</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>LT01</t>
+          <t>NL11</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -7733,23 +7733,23 @@
         </is>
       </c>
       <c r="K184">
-        <v>-0.263</v>
+        <v>1.381</v>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-2</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>LT02</t>
+          <t>NL12</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -7773,23 +7773,23 @@
         </is>
       </c>
       <c r="K185">
-        <v>-0.263</v>
+        <v>1.425</v>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-2</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>LU00</t>
+          <t>NL13</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -7813,23 +7813,23 @@
         </is>
       </c>
       <c r="K186">
-        <v>1.2</v>
+        <v>1.355</v>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-2</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>LV00</t>
+          <t>NL21</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -7853,23 +7853,23 @@
         </is>
       </c>
       <c r="K187">
-        <v>-0.513</v>
+        <v>1.459</v>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-2</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>MT00</t>
+          <t>NL22</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -7893,11 +7893,11 @@
         </is>
       </c>
       <c r="K188">
-        <v>-0.075</v>
+        <v>1.496</v>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-2</t>
         </is>
       </c>
     </row>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>NL11</t>
+          <t>NL23</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -7933,7 +7933,7 @@
         </is>
       </c>
       <c r="K189">
-        <v>1.351</v>
+        <v>1.175</v>
       </c>
       <c r="M189" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>NL12</t>
+          <t>NL31</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="K190">
-        <v>1.351</v>
+        <v>1.208</v>
       </c>
       <c r="M190" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>NL13</t>
+          <t>NL32</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="K191">
-        <v>1.351</v>
+        <v>1.04</v>
       </c>
       <c r="M191" t="inlineStr">
         <is>
@@ -8029,7 +8029,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>NL21</t>
+          <t>NL33</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -8053,7 +8053,7 @@
         </is>
       </c>
       <c r="K192">
-        <v>1.331</v>
+        <v>1.237</v>
       </c>
       <c r="M192" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>NL22</t>
+          <t>NL34</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -8093,7 +8093,7 @@
         </is>
       </c>
       <c r="K193">
-        <v>1.331</v>
+        <v>1.336</v>
       </c>
       <c r="M193" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>NL23</t>
+          <t>NL41</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="K194">
-        <v>1.331</v>
+        <v>1.171</v>
       </c>
       <c r="M194" t="inlineStr">
         <is>
@@ -8149,7 +8149,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>NL31</t>
+          <t>NL42</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -8173,7 +8173,7 @@
         </is>
       </c>
       <c r="K195">
-        <v>1.105</v>
+        <v>1.175</v>
       </c>
       <c r="M195" t="inlineStr">
         <is>
@@ -8184,12 +8184,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>NL32</t>
+          <t>PL21</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="K196">
-        <v>1.105</v>
+        <v>-1.022</v>
       </c>
       <c r="M196" t="inlineStr">
         <is>
@@ -8224,12 +8224,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>NL33</t>
+          <t>PL22</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="K197">
-        <v>1.105</v>
+        <v>-0.8070000000000001</v>
       </c>
       <c r="M197" t="inlineStr">
         <is>
@@ -8264,12 +8264,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>NL34</t>
+          <t>PL41</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -8293,7 +8293,7 @@
         </is>
       </c>
       <c r="K198">
-        <v>1.105</v>
+        <v>-0.643</v>
       </c>
       <c r="M198" t="inlineStr">
         <is>
@@ -8304,12 +8304,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>NL41</t>
+          <t>PL42</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -8333,7 +8333,7 @@
         </is>
       </c>
       <c r="K199">
-        <v>1.228</v>
+        <v>-0.858</v>
       </c>
       <c r="M199" t="inlineStr">
         <is>
@@ -8344,12 +8344,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>NL42</t>
+          <t>PL43</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -8373,7 +8373,7 @@
         </is>
       </c>
       <c r="K200">
-        <v>1.228</v>
+        <v>-1.048</v>
       </c>
       <c r="M200" t="inlineStr">
         <is>
@@ -8389,7 +8389,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>PL21</t>
+          <t>PL51</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -8413,7 +8413,7 @@
         </is>
       </c>
       <c r="K201">
-        <v>-0.401</v>
+        <v>-1.261</v>
       </c>
       <c r="M201" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>PL22</t>
+          <t>PL52</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="K202">
-        <v>-0.48</v>
+        <v>-0.868</v>
       </c>
       <c r="M202" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>PL41</t>
+          <t>PL61</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -8493,7 +8493,7 @@
         </is>
       </c>
       <c r="K203">
-        <v>-0.464</v>
+        <v>-0.89</v>
       </c>
       <c r="M203" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>PL42</t>
+          <t>PL62</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -8533,7 +8533,7 @@
         </is>
       </c>
       <c r="K204">
-        <v>-0.367</v>
+        <v>-1.028</v>
       </c>
       <c r="M204" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>PL43</t>
+          <t>PL63</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -8573,7 +8573,7 @@
         </is>
       </c>
       <c r="K205">
-        <v>-0.411</v>
+        <v>-0.714</v>
       </c>
       <c r="M205" t="inlineStr">
         <is>
@@ -8589,7 +8589,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>PL51</t>
+          <t>PL71</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -8613,7 +8613,7 @@
         </is>
       </c>
       <c r="K206">
-        <v>-0.482</v>
+        <v>-0.6929999999999999</v>
       </c>
       <c r="M206" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>PL52</t>
+          <t>PL72</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -8653,7 +8653,7 @@
         </is>
       </c>
       <c r="K207">
-        <v>-0.298</v>
+        <v>-1.155</v>
       </c>
       <c r="M207" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>PL61</t>
+          <t>PL81</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="K208">
-        <v>-0.338</v>
+        <v>-1.093</v>
       </c>
       <c r="M208" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>PL62</t>
+          <t>PL82</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -8733,7 +8733,7 @@
         </is>
       </c>
       <c r="K209">
-        <v>-0.342</v>
+        <v>-1.125</v>
       </c>
       <c r="M209" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>PL63</t>
+          <t>PL84</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -8773,7 +8773,7 @@
         </is>
       </c>
       <c r="K210">
-        <v>-0.133</v>
+        <v>-0.928</v>
       </c>
       <c r="M210" t="inlineStr">
         <is>
@@ -8789,7 +8789,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>PL71</t>
+          <t>PL91</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -8813,7 +8813,7 @@
         </is>
       </c>
       <c r="K211">
-        <v>-0.66</v>
+        <v>-1.132</v>
       </c>
       <c r="M211" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>PL72</t>
+          <t>PL92</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -8853,7 +8853,7 @@
         </is>
       </c>
       <c r="K212">
-        <v>-0.511</v>
+        <v>-0.911</v>
       </c>
       <c r="M212" t="inlineStr">
         <is>
@@ -8864,12 +8864,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>PL81</t>
+          <t>PT11</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -8893,7 +8893,7 @@
         </is>
       </c>
       <c r="K213">
-        <v>-0.632</v>
+        <v>-0.102</v>
       </c>
       <c r="M213" t="inlineStr">
         <is>
@@ -8904,12 +8904,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>PL82</t>
+          <t>PT15</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="K214">
-        <v>-0.626</v>
+        <v>-0.366</v>
       </c>
       <c r="M214" t="inlineStr">
         <is>
@@ -8944,12 +8944,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>PL84</t>
+          <t>PT16</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -8973,7 +8973,7 @@
         </is>
       </c>
       <c r="K215">
-        <v>-0.456</v>
+        <v>0.057</v>
       </c>
       <c r="M215" t="inlineStr">
         <is>
@@ -8984,12 +8984,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>PL91</t>
+          <t>PT17</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -9013,23 +9013,23 @@
         </is>
       </c>
       <c r="K216">
-        <v>-0.461115</v>
+        <v>0.359</v>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, mismatched NUTS-2 codes)</t>
+          <t>NUTS-2</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>PL92</t>
+          <t>PT18</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -9053,11 +9053,11 @@
         </is>
       </c>
       <c r="K217">
-        <v>-0.461115</v>
+        <v>-0.029</v>
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, mismatched NUTS-2 codes)</t>
+          <t>NUTS-2</t>
         </is>
       </c>
     </row>
@@ -9069,7 +9069,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>PT11</t>
+          <t>PT20</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -9093,7 +9093,7 @@
         </is>
       </c>
       <c r="K218">
-        <v>-0.063</v>
+        <v>0.608</v>
       </c>
       <c r="M218" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>PT15</t>
+          <t>PT30</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -9133,7 +9133,7 @@
         </is>
       </c>
       <c r="K219">
-        <v>-0.292</v>
+        <v>0.24</v>
       </c>
       <c r="M219" t="inlineStr">
         <is>
@@ -9144,12 +9144,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>PT16</t>
+          <t>RO11</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -9173,7 +9173,7 @@
         </is>
       </c>
       <c r="K220">
-        <v>0.07000000000000001</v>
+        <v>-1.02</v>
       </c>
       <c r="M220" t="inlineStr">
         <is>
@@ -9184,12 +9184,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>PT17</t>
+          <t>RO12</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -9213,7 +9213,7 @@
         </is>
       </c>
       <c r="K221">
-        <v>0.108</v>
+        <v>-0.8139999999999999</v>
       </c>
       <c r="M221" t="inlineStr">
         <is>
@@ -9224,12 +9224,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>PT18</t>
+          <t>RO21</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -9253,7 +9253,7 @@
         </is>
       </c>
       <c r="K222">
-        <v>0.247</v>
+        <v>-1.432</v>
       </c>
       <c r="M222" t="inlineStr">
         <is>
@@ -9264,12 +9264,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>PT20</t>
+          <t>RO22</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="K223">
-        <v>0.008999999999999999</v>
+        <v>-1.5</v>
       </c>
       <c r="M223" t="inlineStr">
         <is>
@@ -9304,12 +9304,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>PT30</t>
+          <t>RO31</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -9333,7 +9333,7 @@
         </is>
       </c>
       <c r="K224">
-        <v>0.169</v>
+        <v>-1.433</v>
       </c>
       <c r="M224" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>RO11</t>
+          <t>RO32</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -9373,7 +9373,7 @@
         </is>
       </c>
       <c r="K225">
-        <v>-1.849</v>
+        <v>-1.542</v>
       </c>
       <c r="M225" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>RO12</t>
+          <t>RO41</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -9413,7 +9413,7 @@
         </is>
       </c>
       <c r="K226">
-        <v>-1.434</v>
+        <v>-1.183</v>
       </c>
       <c r="M226" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>RO21</t>
+          <t>RO42</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -9453,7 +9453,7 @@
         </is>
       </c>
       <c r="K227">
-        <v>-1.58</v>
+        <v>-1.222</v>
       </c>
       <c r="M227" t="inlineStr">
         <is>
@@ -9464,12 +9464,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>RO22</t>
+          <t>SE11</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="K228">
-        <v>-1.973</v>
+        <v>1.289</v>
       </c>
       <c r="M228" t="inlineStr">
         <is>
@@ -9504,12 +9504,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>RO31</t>
+          <t>SE12</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
@@ -9533,7 +9533,7 @@
         </is>
       </c>
       <c r="K229">
-        <v>-1.104</v>
+        <v>1.146</v>
       </c>
       <c r="M229" t="inlineStr">
         <is>
@@ -9544,12 +9544,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>RO32</t>
+          <t>SE21</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
@@ -9573,7 +9573,7 @@
         </is>
       </c>
       <c r="K230">
-        <v>-1.578</v>
+        <v>1.723</v>
       </c>
       <c r="M230" t="inlineStr">
         <is>
@@ -9584,12 +9584,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>RO41</t>
+          <t>SE22</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="K231">
-        <v>-1.615</v>
+        <v>1.079</v>
       </c>
       <c r="M231" t="inlineStr">
         <is>
@@ -9624,12 +9624,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>RO42</t>
+          <t>SE23</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -9653,7 +9653,7 @@
         </is>
       </c>
       <c r="K232">
-        <v>-1.341</v>
+        <v>1.353</v>
       </c>
       <c r="M232" t="inlineStr">
         <is>
@@ -9669,7 +9669,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>SE11</t>
+          <t>SE31</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -9693,11 +9693,11 @@
         </is>
       </c>
       <c r="K233">
-        <v>1.40333</v>
+        <v>1.36</v>
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-2</t>
         </is>
       </c>
     </row>
@@ -9709,7 +9709,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>SE12</t>
+          <t>SE32</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -9733,11 +9733,11 @@
         </is>
       </c>
       <c r="K234">
-        <v>1.40333</v>
+        <v>1.767</v>
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-2</t>
         </is>
       </c>
     </row>
@@ -9749,7 +9749,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>SE21</t>
+          <t>SE33</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -9773,23 +9773,23 @@
         </is>
       </c>
       <c r="K235">
-        <v>1.40333</v>
+        <v>1.651</v>
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-2</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>SE22</t>
+          <t>SI03</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -9813,23 +9813,23 @@
         </is>
       </c>
       <c r="K236">
-        <v>1.40333</v>
+        <v>-0.216</v>
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-2</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>SE23</t>
+          <t>SI04</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -9853,23 +9853,23 @@
         </is>
       </c>
       <c r="K237">
-        <v>1.40333</v>
+        <v>0.099</v>
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-2</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>SE31</t>
+          <t>SK01</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -9893,23 +9893,23 @@
         </is>
       </c>
       <c r="K238">
-        <v>1.40333</v>
+        <v>-1.115</v>
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-2</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>SE32</t>
+          <t>SK02</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -9933,23 +9933,23 @@
         </is>
       </c>
       <c r="K239">
-        <v>1.40333</v>
+        <v>-0.634</v>
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-2</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>SE33</t>
+          <t>SK03</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -9973,23 +9973,23 @@
         </is>
       </c>
       <c r="K240">
-        <v>1.40333</v>
+        <v>-0.551</v>
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>NUTS-0 (national, replicated)</t>
+          <t>NUTS-2</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>SI03</t>
+          <t>SK04</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -10013,209 +10013,9 @@
         </is>
       </c>
       <c r="K241">
-        <v>-0.293</v>
+        <v>-1.074</v>
       </c>
       <c r="M241" t="inlineStr">
-        <is>
-          <t>NUTS-0 (national, replicated)</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>SI04</t>
-        </is>
-      </c>
-      <c r="G242" t="inlineStr">
-        <is>
-          <t>Vulnerability</t>
-        </is>
-      </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>Institutions</t>
-        </is>
-      </c>
-      <c r="I242" t="inlineStr">
-        <is>
-          <t>QoG_Index</t>
-        </is>
-      </c>
-      <c r="J242" t="inlineStr">
-        <is>
-          <t>EQI Score</t>
-        </is>
-      </c>
-      <c r="K242">
-        <v>-0.293</v>
-      </c>
-      <c r="M242" t="inlineStr">
-        <is>
-          <t>NUTS-0 (national, replicated)</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>SK</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>SK01</t>
-        </is>
-      </c>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>Vulnerability</t>
-        </is>
-      </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>Institutions</t>
-        </is>
-      </c>
-      <c r="I243" t="inlineStr">
-        <is>
-          <t>QoG_Index</t>
-        </is>
-      </c>
-      <c r="J243" t="inlineStr">
-        <is>
-          <t>EQI Score</t>
-        </is>
-      </c>
-      <c r="K243">
-        <v>-0.954</v>
-      </c>
-      <c r="M243" t="inlineStr">
-        <is>
-          <t>NUTS-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>SK</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>SK02</t>
-        </is>
-      </c>
-      <c r="G244" t="inlineStr">
-        <is>
-          <t>Vulnerability</t>
-        </is>
-      </c>
-      <c r="H244" t="inlineStr">
-        <is>
-          <t>Institutions</t>
-        </is>
-      </c>
-      <c r="I244" t="inlineStr">
-        <is>
-          <t>QoG_Index</t>
-        </is>
-      </c>
-      <c r="J244" t="inlineStr">
-        <is>
-          <t>EQI Score</t>
-        </is>
-      </c>
-      <c r="K244">
-        <v>-1.013</v>
-      </c>
-      <c r="M244" t="inlineStr">
-        <is>
-          <t>NUTS-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>SK</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>SK03</t>
-        </is>
-      </c>
-      <c r="G245" t="inlineStr">
-        <is>
-          <t>Vulnerability</t>
-        </is>
-      </c>
-      <c r="H245" t="inlineStr">
-        <is>
-          <t>Institutions</t>
-        </is>
-      </c>
-      <c r="I245" t="inlineStr">
-        <is>
-          <t>QoG_Index</t>
-        </is>
-      </c>
-      <c r="J245" t="inlineStr">
-        <is>
-          <t>EQI Score</t>
-        </is>
-      </c>
-      <c r="K245">
-        <v>-0.626</v>
-      </c>
-      <c r="M245" t="inlineStr">
-        <is>
-          <t>NUTS-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>SK</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>SK04</t>
-        </is>
-      </c>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>Vulnerability</t>
-        </is>
-      </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>Institutions</t>
-        </is>
-      </c>
-      <c r="I246" t="inlineStr">
-        <is>
-          <t>QoG_Index</t>
-        </is>
-      </c>
-      <c r="J246" t="inlineStr">
-        <is>
-          <t>EQI Score</t>
-        </is>
-      </c>
-      <c r="K246">
-        <v>-0.681</v>
-      </c>
-      <c r="M246" t="inlineStr">
         <is>
           <t>NUTS-2</t>
         </is>
